--- a/201025_Results_Cali/output/m2/21102025_mod2_by_ses.xlsx
+++ b/201025_Results_Cali/output/m2/21102025_mod2_by_ses.xlsx
@@ -3061,26 +3061,26 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12 (13.3%)</t>
+          <t>5 (5.6%)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17 (10.9%)</t>
+          <t>6 (3.8%)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>26 (13.9%)</t>
+          <t>11 (5.9%)</t>
         </is>
       </c>
       <c r="G78">
-        <v>0.1836</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="79">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cuidado y familia (centro educativo, niños/as o jóvenes)</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>2 (2.2%)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="G79">
-        <v>0.1836</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="80">
@@ -3131,26 +3131,26 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cuidado y familia (otro lugar, niños/as o jóvenes)</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>3 (3.3%)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>9 (5.8%)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1 (0.5%)</t>
+          <t>5 (2.7%)</t>
         </is>
       </c>
       <c r="G80">
-        <v>0.1836</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="81">
@@ -3166,26 +3166,26 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estudio</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5 (5.6%)</t>
+          <t>11 (12.2%)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>6 (3.8%)</t>
+          <t>38 (24.4%)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>11 (5.9%)</t>
+          <t>28 (15.0%)</t>
         </is>
       </c>
       <c r="G81">
-        <v>0.1836</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="82">
@@ -3201,26 +3201,26 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Trabajo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2 (2.2%)</t>
+          <t>57 (63.3%)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2 (1.3%)</t>
+          <t>78 (50.0%)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1 (0.5%)</t>
+          <t>108 (57.8%)</t>
         </is>
       </c>
       <c r="G82">
-        <v>0.1836</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="83">
@@ -3236,26 +3236,26 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>14 (15.6%)</t>
+          <t>2 (2.2%)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>47 (30.1%)</t>
+          <t>4 (2.6%)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>33 (17.6%)</t>
+          <t>11 (5.9%)</t>
         </is>
       </c>
       <c r="G83">
-        <v>0.1836</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="84">
@@ -3271,26 +3271,26 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trabajo</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>57 (63.3%)</t>
+          <t>10 (11.1%)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>78 (50.0%)</t>
+          <t>15 (9.6%)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>108 (57.8%)</t>
+          <t>17 (9.1%)</t>
         </is>
       </c>
       <c r="G84">
-        <v>0.1836</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="85">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G85">
-        <v>0.1836</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="86">
